--- a/projects/pnw-banks/pnw_banks_comp.xlsx
+++ b/projects/pnw-banks/pnw_banks_comp.xlsx
@@ -1,209 +1,76 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Comp Table" sheetId="1" r:id="rId1"/>
-    <sheet name="Methodology" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comp Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
-  <si>
-    <t>Pacific Northwest Regional Banks — Comp Table</t>
-  </si>
-  <si>
-    <t>Fundamentals: SEC EDGAR XBRL (most recent 10-K). Market: Yahoo Finance.</t>
-  </si>
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>COLB
-Columbia Banking System</t>
-  </si>
-  <si>
-    <t>BANR
-Banner Corporation</t>
-  </si>
-  <si>
-    <t>HFWA
-Heritage Financial</t>
-  </si>
-  <si>
-    <t>Scale ($M, most recent FY)</t>
-  </si>
-  <si>
-    <t>Total Assets</t>
-  </si>
-  <si>
-    <t>Total Deposits</t>
-  </si>
-  <si>
-    <t>Net Loans</t>
-  </si>
-  <si>
-    <t>Stockholders' Equity</t>
-  </si>
-  <si>
-    <t>Net Income</t>
-  </si>
-  <si>
-    <t>Net Interest Income</t>
-  </si>
-  <si>
-    <t>Profitability &amp; Balance Sheet Ratios</t>
-  </si>
-  <si>
-    <t>ROA</t>
-  </si>
-  <si>
-    <t>ROE</t>
-  </si>
-  <si>
-    <t>Loan-to-Deposit</t>
-  </si>
-  <si>
-    <t>Equity / Assets (Lev.)</t>
-  </si>
-  <si>
-    <t>Est. NIM (NII / Assets)</t>
-  </si>
-  <si>
-    <t>Market Multiples (current)</t>
-  </si>
-  <si>
-    <t>Share Price ($)</t>
-  </si>
-  <si>
-    <t>Market Cap ($M)</t>
-  </si>
-  <si>
-    <t>P/E (trailing)</t>
-  </si>
-  <si>
-    <t>P/B</t>
-  </si>
-  <si>
-    <t>Dividend Yield</t>
-  </si>
-  <si>
-    <t>Beta</t>
-  </si>
-  <si>
-    <t>Data Sources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Balance sheet + P&amp;L:  SEC EDGAR XBRL companyfacts API (data.sec.gov, free, no auth)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Market multiples:     Yahoo Finance (yfinance)</t>
-  </si>
-  <si>
-    <t>Metric Definitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ROA           = Net Income / Total Assets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ROE           = Net Income / Stockholders' Equity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Loan/Deposit  = Net Loans / Total Deposits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Equity/Assets = Stockholders' Equity / Total Assets  (simple leverage proxy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Est. NIM      = Net Interest Income / Total Assets   (approximation; true NIM uses average earning assets)</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  'n/a' indicates the XBRL tag was not found or reported differently; banks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  sometimes file loans under different us-gaap tags. See first_available() in</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  build_comp_table.py for the fallback tag list.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Fiscal-year fields come from the most recent annual 10-K filing per bank.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  All three PNW banks report on a calendar-year basis.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
-    <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
   <fonts count="6">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FF1A1A1A"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1A1A1A"/>
+      <sz val="14"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF555555"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <i val="1"/>
+      <color rgb="FF555555"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1A1A1A"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1A1A1A"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -227,7 +94,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -250,38 +117,157 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -569,297 +555,356 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.7109375" customWidth="1"/>
-    <col min="2" max="4" width="17.7109375" customWidth="1"/>
+    <col width="32.7109375" customWidth="1" min="1" max="1"/>
+    <col width="17.7109375" customWidth="1" min="2" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pacific Northwest Regional Banks — Comp Table</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals: SEC EDGAR XBRL (most recent 10-K). Market: Yahoo Finance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>COLB
+Columbia Banking System</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>BANR
+Banner Corporation</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>HFWA
+Heritage Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Scale ($M, most recent FY)</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="10" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
         <v>66832</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="6" t="n">
         <v>16354.488</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="6" t="n">
         <v>6967.35</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6">
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Total Deposits</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
         <v>54211</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="6" t="n">
         <v>13743.146</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="6" t="n">
         <v>5920.199</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6">
-        <v>37001.08</v>
-      </c>
-      <c r="C8" s="6">
-        <v>10660.812</v>
-      </c>
-      <c r="D8" s="6">
-        <v>4398.462</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="6">
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Net Loans</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>47310</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>11561.411</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>4730.682</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Stockholders' Equity</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>7840</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="6" t="n">
         <v>1946.297</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="6" t="n">
         <v>921.504</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="6">
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>550</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="6" t="n">
         <v>195.382</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="6" t="n">
         <v>67.532</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="6">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Net Interest Income</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
         <v>2003</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="6" t="n">
         <v>587.919</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="6" t="n">
         <v>224.405</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="7">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Profitability &amp; Balance Sheet Ratios</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
         <v>0.00822959061527412</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="11" t="n">
         <v>0.01194669010732711</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="11" t="n">
         <v>0.009692637803469038</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="7">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>ROE</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
         <v>0.07015306122448979</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="11" t="n">
         <v>0.1003865288802274</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="11" t="n">
         <v>0.07328454352883981</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="7">
-        <v>0.6825382302484736</v>
-      </c>
-      <c r="C15" s="7">
-        <v>0.7757184563126958</v>
-      </c>
-      <c r="D15" s="7">
-        <v>0.7429584714973264</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="7">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Loan-to-Deposit</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>0.8727011123203778</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>0.8412492307074377</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>0.7990748283968158</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Equity / Assets (Lev.)</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
         <v>0.1173090734977256</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="11" t="n">
         <v>0.1190069050159198</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="11" t="n">
         <v>0.1322603285323688</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" s="7">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Est. NIM (NII / Assets)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
         <v>0.02997067273162557</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="11" t="n">
         <v>0.03594848093073901</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="11" t="n">
         <v>0.03220808485292113</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19" s="8">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Market Multiples (current)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="10" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Share Price ($)</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
         <v>29.65</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="12" t="n">
         <v>67.76000000000001</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="12" t="n">
         <v>27.7</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="6">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Market Cap ($M)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
         <v>8598.318079999999</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="6" t="n">
         <v>2295.37664</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="6" t="n">
         <v>1139.331456</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="8">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>P/E (trailing)</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
         <v>12.891304</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="12" t="n">
         <v>11.407408</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="12" t="n">
         <v>14.132653</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" s="8">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>P/B</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
         <v>1.1172658</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="12" t="n">
         <v>1.1871058</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="12" t="n">
         <v>1.0209347</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="7">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Dividend Yield</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n">
         <v>0.0492</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="11" t="n">
         <v>0.0309</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="11" t="n">
         <v>0.0351</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="8">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Beta</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n">
         <v>0.6830000000000001</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24" s="12" t="n">
         <v>0.843</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="12" t="n">
         <v>0.484</v>
       </c>
     </row>
@@ -874,86 +919,127 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="120.7109375" customWidth="1"/>
+    <col width="120.7109375" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>40</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Data Sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Balance sheet + P&amp;L:  SEC EDGAR XBRL companyfacts API (data.sec.gov, free, no auth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Market multiples:     Yahoo Finance (yfinance)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Metric Definitions</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ROA           = Net Income / Total Assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ROE           = Net Income / Stockholders' Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Loan/Deposit  = Net Loans / Total Deposits</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Equity/Assets = Stockholders' Equity / Total Assets  (simple leverage proxy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Est. NIM      = Net Interest Income / Total Assets   (approximation; true NIM uses average earning assets)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  'n/a' indicates the XBRL tag was not found or reported differently; banks</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  sometimes file loans under different us-gaap tags. See first_available() in</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  build_comp_table.py for the fallback tag list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fiscal-year fields come from the most recent annual 10-K filing per bank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  All three PNW banks report on a calendar-year basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Correction (October 2026): Net Loans now use each bank's FY2025 10-K value. The April build picked an older loans tag for COLB (FY2023), BANR (FY2023) and HFWA (FY2020); other figures unchanged.</t>
+        </is>
       </c>
     </row>
   </sheetData>
